--- a/data/extra_material/cuq_questions.xlsx
+++ b/data/extra_material/cuq_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\Chatbot-Evaluation-Framework\data\extra_material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\CEP-guide\data\extra_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14005294-A547-42B8-A3CB-B9A10F1569B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D259AE11-17D0-4B1A-B448-A62A12523D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>The chatbot's personality was realistic and engaging.</t>
   </si>
@@ -123,10 +123,16 @@
     <t>cuq16</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>question</t>
+    <t>Strongly Disagree (1); Disagree (2);  Neutral (3);  Agree (4);  Strongly Agree (5)</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Question</t>
   </si>
 </sst>
 </file>
@@ -459,147 +465,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.53125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
